--- a/data/trans_dic/PCS12_SP_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R3-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12)</t>
+          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,27</t>
+          <t>2,75; 6,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,61</t>
+          <t>2,2; 5,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,71</t>
+          <t>0,72; 3,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,18</t>
+          <t>0,04; 3,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 7,92</t>
+          <t>3,71; 7,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 9,27</t>
+          <t>4,43; 9,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,2</t>
+          <t>2,84; 7,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 10,31</t>
+          <t>2,53; 10,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 6,26</t>
+          <t>3,48; 6,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,66</t>
+          <t>3,62; 6,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,67</t>
+          <t>2,01; 4,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,58</t>
+          <t>1,64; 5,47</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,97</t>
+          <t>2,81; 6,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 8,67</t>
+          <t>4,5; 8,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,78</t>
+          <t>3,26; 7,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 14,13</t>
+          <t>6,64; 13,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 11,89</t>
+          <t>7,2; 11,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 9,29</t>
+          <t>4,88; 9,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 9,4</t>
+          <t>4,84; 9,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 9,68</t>
+          <t>4,04; 9,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,28; 8,16</t>
+          <t>5,25; 8,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,22</t>
+          <t>5,37; 8,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 7,4</t>
+          <t>4,59; 7,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 10,73</t>
+          <t>5,99; 10,54</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,06</t>
+          <t>5,3; 9,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,97; 11,39</t>
+          <t>7,13; 11,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 9,45</t>
+          <t>5,49; 9,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,28; 15,28</t>
+          <t>9,45; 15,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,34; 16,77</t>
+          <t>11,4; 16,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,24; 17,85</t>
+          <t>12,5; 17,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,77</t>
+          <t>8,14; 13,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,49; 17,52</t>
+          <t>12,43; 17,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,89; 12,24</t>
+          <t>8,87; 12,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,4; 14,19</t>
+          <t>10,42; 13,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,58</t>
+          <t>7,38; 10,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,53; 15,49</t>
+          <t>11,43; 15,46</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 14,9</t>
+          <t>8,6; 14,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,55; 16,33</t>
+          <t>10,28; 15,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,98; 17,96</t>
+          <t>12,2; 18,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,41; 74,43</t>
+          <t>18,21; 75,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,64; 28,38</t>
+          <t>20,61; 27,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 23,38</t>
+          <t>16,51; 23,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,15; 22,74</t>
+          <t>16,17; 22,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,46; 26,82</t>
+          <t>20,16; 26,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,34; 20,04</t>
+          <t>15,57; 20,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,23; 18,71</t>
+          <t>14,42; 18,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,92; 19,05</t>
+          <t>15,07; 19,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,09; 60,09</t>
+          <t>21,09; 60,75</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,09; 33,63</t>
+          <t>24,32; 33,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,68; 28,2</t>
+          <t>19,61; 28,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,56; 28,58</t>
+          <t>19,87; 28,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,2; 35,59</t>
+          <t>28,27; 35,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,18; 38,21</t>
+          <t>28,9; 38,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,76; 48,56</t>
+          <t>39,01; 48,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,92; 41,09</t>
+          <t>32,08; 40,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,51; 40,73</t>
+          <t>34,68; 40,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,14; 34,59</t>
+          <t>28,12; 34,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,97; 37,62</t>
+          <t>30,65; 37,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,29; 33,73</t>
+          <t>27,03; 33,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,07; 37,05</t>
+          <t>32,2; 37,18</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,57; 43,92</t>
+          <t>33,1; 44,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37,32; 49,36</t>
+          <t>36,92; 49,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,84; 38,99</t>
+          <t>28,56; 38,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,38; 36,08</t>
+          <t>28,39; 35,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55,98; 66,17</t>
+          <t>56,38; 66,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56,11; 66,64</t>
+          <t>56,21; 66,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,63; 57,63</t>
+          <t>46,89; 57,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,66; 48,99</t>
+          <t>12,85; 48,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47,06; 54,72</t>
+          <t>46,89; 54,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48,33; 56,56</t>
+          <t>48,61; 56,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39,53; 46,98</t>
+          <t>39,71; 47,39</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,72; 41,1</t>
+          <t>17,08; 41,11</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>60,21; 72,69</t>
+          <t>60,48; 73,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,18; 75,93</t>
+          <t>63,4; 75,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55,52; 66,54</t>
+          <t>55,7; 66,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52,7; 61,63</t>
+          <t>52,9; 62,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,12; 85,33</t>
+          <t>76,02; 84,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,3; 87,1</t>
+          <t>79,66; 87,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,36; 79,72</t>
+          <t>69,67; 79,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>75,84; 81,51</t>
+          <t>75,6; 81,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71,61; 79,02</t>
+          <t>71,28; 78,94</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74,77; 81,73</t>
+          <t>74,86; 81,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65,55; 73,73</t>
+          <t>66,04; 73,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,61; 72,54</t>
+          <t>67,46; 72,62</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,65; 17,11</t>
+          <t>14,48; 17,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,72; 19,22</t>
+          <t>16,61; 19,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,43; 17,96</t>
+          <t>15,5; 18,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,12; 46,85</t>
+          <t>21,09; 42,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,62; 28,75</t>
+          <t>25,71; 28,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,55; 30,6</t>
+          <t>27,49; 30,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,67; 27,76</t>
+          <t>24,69; 27,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>23,57; 30,69</t>
+          <t>22,89; 30,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,52; 22,62</t>
+          <t>20,48; 22,61</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22,61; 24,69</t>
+          <t>22,64; 24,7</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20,46; 22,54</t>
+          <t>20,49; 22,52</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,18; 35,49</t>
+          <t>24,29; 36,84</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12)</t>
+          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13522; 30981</t>
+          <t>13601; 32100</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9248; 25495</t>
+          <t>9974; 25404</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3057; 15570</t>
+          <t>3031; 15221</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>167; 16710</t>
+          <t>167; 15295</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16831; 37027</t>
+          <t>17344; 36917</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19190; 39876</t>
+          <t>19043; 40490</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11557; 28513</t>
+          <t>11224; 27899</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7469; 32132</t>
+          <t>7891; 31247</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35280; 60181</t>
+          <t>33497; 60286</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32693; 58866</t>
+          <t>32013; 58985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17887; 38094</t>
+          <t>16384; 37361</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11509; 39724</t>
+          <t>11651; 38934</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20566; 43926</t>
+          <t>20687; 44780</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32190; 59577</t>
+          <t>30887; 58229</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19057; 40048</t>
+          <t>19241; 41309</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28986; 59860</t>
+          <t>28107; 58552</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44485; 74361</t>
+          <t>45036; 74889</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30471; 56700</t>
+          <t>29804; 55777</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28152; 52956</t>
+          <t>27262; 52025</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20948; 49474</t>
+          <t>20625; 49337</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>71853; 111000</t>
+          <t>71460; 108870</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69318; 106685</t>
+          <t>69635; 107210</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52045; 85368</t>
+          <t>53007; 86361</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56373; 100286</t>
+          <t>56005; 98465</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32572; 57891</t>
+          <t>33826; 59321</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47552; 77638</t>
+          <t>48585; 77393</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36481; 63257</t>
+          <t>36754; 62737</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49679; 81803</t>
+          <t>50592; 81980</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78187; 115686</t>
+          <t>78606; 115599</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87033; 126877</t>
+          <t>88836; 125981</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53932; 84440</t>
+          <t>53846; 86064</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>67650; 94922</t>
+          <t>67316; 95021</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>118072; 162559</t>
+          <t>117865; 163355</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144774; 197661</t>
+          <t>145173; 193807</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>97328; 140714</t>
+          <t>98168; 139323</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>124233; 166809</t>
+          <t>123097; 166569</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44938; 77366</t>
+          <t>44630; 73943</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64872; 100383</t>
+          <t>63209; 98135</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77411; 116041</t>
+          <t>78788; 116984</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>163037; 659220</t>
+          <t>161269; 666980</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>106415; 146332</t>
+          <t>106273; 143700</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>103774; 144046</t>
+          <t>101736; 142381</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>104838; 147625</t>
+          <t>104953; 143881</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>145129; 190219</t>
+          <t>143019; 190360</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>158782; 207323</t>
+          <t>161073; 209366</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>175176; 230237</t>
+          <t>177510; 231270</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>193206; 246734</t>
+          <t>195113; 249619</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>336329; 958395</t>
+          <t>336447; 969010</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>93149; 130052</t>
+          <t>94054; 129287</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>84524; 121092</t>
+          <t>84193; 121900</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98261; 136580</t>
+          <t>94956; 135609</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156478; 197507</t>
+          <t>156905; 198650</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>117899; 154380</t>
+          <t>116772; 156454</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>173560; 217446</t>
+          <t>174676; 219183</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>158572; 204148</t>
+          <t>159371; 203524</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>188286; 222222</t>
+          <t>189213; 222124</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>222519; 273476</t>
+          <t>222334; 275859</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>271708; 329998</t>
+          <t>268887; 327409</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>265972; 328795</t>
+          <t>263454; 326154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>352920; 407783</t>
+          <t>354418; 409147</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>95291; 128494</t>
+          <t>96832; 129558</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>115619; 152924</t>
+          <t>114379; 152066</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>96431; 130346</t>
+          <t>95484; 129110</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>103233; 131257</t>
+          <t>103274; 130869</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>191962; 226932</t>
+          <t>193346; 227553</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>198627; 235917</t>
+          <t>198992; 235276</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>176147; 217690</t>
+          <t>177117; 216758</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>82882; 297203</t>
+          <t>77926; 296148</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>299059; 347739</t>
+          <t>297966; 348874</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>320813; 375434</t>
+          <t>322666; 375313</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>281500; 334543</t>
+          <t>282797; 337427</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>171971; 398854</t>
+          <t>165739; 398959</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>126366; 152570</t>
+          <t>126934; 153984</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>160353; 189701</t>
+          <t>158402; 188788</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>142682; 170998</t>
+          <t>143159; 170712</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>147776; 172815</t>
+          <t>148353; 173863</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>254163; 284935</t>
+          <t>253835; 283381</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>308466; 338789</t>
+          <t>309877; 340252</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>277556; 319013</t>
+          <t>278802; 319052</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>316778; 340479</t>
+          <t>315801; 338472</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>389422; 429687</t>
+          <t>387611; 429286</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>477682; 522140</t>
+          <t>478221; 522580</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>430787; 484550</t>
+          <t>434021; 482680</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>472025; 506408</t>
+          <t>470967; 506944</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>479996; 560644</t>
+          <t>474454; 560810</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>573040; 658524</t>
+          <t>569321; 661015</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>523746; 609668</t>
+          <t>525968; 616499</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>727315; 1613373</t>
+          <t>726198; 1480569</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>865860; 971428</t>
+          <t>868738; 973390</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>980169; 1088966</t>
+          <t>978146; 1093802</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>874369; 984036</t>
+          <t>875309; 985535</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>858752; 1118072</t>
+          <t>833870; 1116157</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1365870; 1505658</t>
+          <t>1362956; 1504916</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1579453; 1724670</t>
+          <t>1581308; 1725508</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1419595; 1563796</t>
+          <t>1422095; 1562434</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1713593; 2514992</t>
+          <t>1721211; 2611019</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/PCS12_SP_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R3-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,5</t>
+          <t>2,64; 6,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,59</t>
+          <t>2,12; 5,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,63</t>
+          <t>0,75; 3,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,82</t>
+          <t>0,36; 4,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,9</t>
+          <t>3,52; 7,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 9,41</t>
+          <t>4,42; 9,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 7,05</t>
+          <t>2,89; 7,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 10,03</t>
+          <t>3,86; 12,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,27</t>
+          <t>3,66; 6,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,67</t>
+          <t>3,68; 6,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,58</t>
+          <t>2,15; 4,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,47</t>
+          <t>2,38; 6,46</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,09</t>
+          <t>2,97; 6,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,47</t>
+          <t>4,58; 8,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,0</t>
+          <t>3,19; 6,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 13,82</t>
+          <t>7,11; 13,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 11,97</t>
+          <t>7,16; 11,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 9,14</t>
+          <t>5,06; 9,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 9,23</t>
+          <t>4,88; 9,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,66</t>
+          <t>5,18; 10,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,0</t>
+          <t>5,18; 8,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 8,26</t>
+          <t>5,42; 8,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,48</t>
+          <t>4,43; 7,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 10,54</t>
+          <t>6,7; 10,61</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,29</t>
+          <t>5,11; 9,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,35</t>
+          <t>7,05; 11,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 9,38</t>
+          <t>5,57; 9,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,45; 15,31</t>
+          <t>8,6; 13,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,4; 16,76</t>
+          <t>11,3; 16,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,5; 17,72</t>
+          <t>12,26; 17,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,14; 13,01</t>
+          <t>8,15; 12,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,43; 17,54</t>
+          <t>12,56; 17,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,87; 12,3</t>
+          <t>8,71; 12,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,42; 13,92</t>
+          <t>10,39; 14,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 10,47</t>
+          <t>7,38; 10,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,43; 15,46</t>
+          <t>11,3; 15,01</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,6; 14,24</t>
+          <t>8,71; 14,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 15,97</t>
+          <t>10,47; 16,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 18,11</t>
+          <t>12,48; 17,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,21; 75,31</t>
+          <t>16,82; 22,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,61; 27,87</t>
+          <t>20,72; 28,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,51; 23,11</t>
+          <t>16,78; 23,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,17; 22,17</t>
+          <t>15,99; 22,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,16; 26,84</t>
+          <t>21,59; 26,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,57; 20,23</t>
+          <t>15,36; 19,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,42; 18,79</t>
+          <t>14,22; 18,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,07; 19,27</t>
+          <t>14,99; 19,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,09; 60,75</t>
+          <t>20,13; 24,21</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,32; 33,43</t>
+          <t>24,14; 33,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,61; 28,39</t>
+          <t>20,1; 28,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,87; 28,37</t>
+          <t>19,92; 28,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,27; 35,8</t>
+          <t>26,65; 33,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,9; 38,73</t>
+          <t>28,99; 38,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,01; 48,95</t>
+          <t>38,88; 48,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,08; 40,96</t>
+          <t>31,92; 41,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,68; 40,71</t>
+          <t>34,65; 41,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,12; 34,89</t>
+          <t>28,11; 34,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,65; 37,32</t>
+          <t>30,64; 37,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,03; 33,46</t>
+          <t>27,01; 33,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,2; 37,18</t>
+          <t>31,8; 36,52</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>39,97%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,1; 44,28</t>
+          <t>32,94; 43,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36,92; 49,09</t>
+          <t>37,53; 49,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,56; 38,62</t>
+          <t>28,3; 38,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,39; 35,98</t>
+          <t>27,62; 35,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56,38; 66,35</t>
+          <t>55,89; 65,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56,21; 66,46</t>
+          <t>56,04; 66,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,89; 57,38</t>
+          <t>46,61; 57,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,85; 48,82</t>
+          <t>44,52; 50,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46,89; 54,9</t>
+          <t>46,72; 54,27</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48,61; 56,54</t>
+          <t>48,58; 56,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39,71; 47,39</t>
+          <t>40,02; 47,46</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,08; 41,11</t>
+          <t>37,45; 42,56</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,76%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>60,48; 73,37</t>
+          <t>60,21; 72,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63,4; 75,56</t>
+          <t>63,65; 76,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55,7; 66,43</t>
+          <t>55,89; 67,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52,9; 62,0</t>
+          <t>52,83; 62,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,02; 84,87</t>
+          <t>76,17; 84,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,66; 87,47</t>
+          <t>79,29; 87,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,67; 79,73</t>
+          <t>69,98; 79,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>75,6; 81,03</t>
+          <t>75,3; 81,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71,28; 78,94</t>
+          <t>71,88; 79,04</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74,86; 81,8</t>
+          <t>74,71; 81,72</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66,04; 73,45</t>
+          <t>65,94; 73,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,46; 72,62</t>
+          <t>67,18; 72,32</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,48; 17,12</t>
+          <t>14,68; 17,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,61; 19,29</t>
+          <t>16,44; 19,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,5; 18,16</t>
+          <t>15,46; 18,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,09; 42,99</t>
+          <t>19,83; 22,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,71; 28,81</t>
+          <t>25,72; 28,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,49; 30,74</t>
+          <t>27,51; 30,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,69; 27,8</t>
+          <t>24,49; 27,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,89; 30,63</t>
+          <t>29,1; 31,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,48; 22,61</t>
+          <t>20,61; 22,62</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22,64; 24,7</t>
+          <t>22,65; 24,66</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20,49; 22,52</t>
+          <t>20,43; 22,54</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,29; 36,84</t>
+          <t>24,92; 26,82</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>25477</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22018</t>
+          <t>31498</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13601; 32100</t>
+          <t>13042; 30863</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9974; 25404</t>
+          <t>9642; 26178</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3031; 15221</t>
+          <t>3130; 16023</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>167; 15295</t>
+          <t>1459; 17049</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17344; 36917</t>
+          <t>16433; 35540</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19043; 40490</t>
+          <t>18998; 40978</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11224; 27899</t>
+          <t>11445; 28253</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7891; 31247</t>
+          <t>13926; 43343</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33497; 60286</t>
+          <t>35149; 60114</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32013; 58985</t>
+          <t>32550; 58853</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16384; 37361</t>
+          <t>17568; 37509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11651; 38934</t>
+          <t>18262; 49683</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41415</t>
+          <t>46768</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34706</t>
+          <t>36517</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76121</t>
+          <t>83285</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20687; 44780</t>
+          <t>21847; 45704</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30887; 58229</t>
+          <t>31436; 59391</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19241; 41309</t>
+          <t>18813; 41094</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28107; 58552</t>
+          <t>33886; 66580</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45036; 74889</t>
+          <t>44757; 74138</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29804; 55777</t>
+          <t>30851; 57036</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27262; 52025</t>
+          <t>27521; 52095</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20625; 49337</t>
+          <t>25941; 50938</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>71460; 108870</t>
+          <t>70463; 109857</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69635; 107210</t>
+          <t>70341; 106314</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53007; 86361</t>
+          <t>51104; 85792</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56005; 98465</t>
+          <t>65518; 103735</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>68508</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79704</t>
+          <t>92150</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>144074</t>
+          <t>160658</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33826; 59321</t>
+          <t>32622; 58403</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48585; 77393</t>
+          <t>48040; 80134</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36754; 62737</t>
+          <t>37243; 63729</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50592; 81980</t>
+          <t>53301; 85227</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78606; 115599</t>
+          <t>77975; 112601</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88836; 125981</t>
+          <t>87156; 125898</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53846; 86064</t>
+          <t>53891; 83801</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>67316; 95021</t>
+          <t>78025; 108041</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>117865; 163355</t>
+          <t>115725; 162795</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145173; 193807</t>
+          <t>144651; 195615</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98168; 139323</t>
+          <t>98215; 141819</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>123097; 166569</t>
+          <t>140313; 186292</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369498</t>
+          <t>137877</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>168444</t>
+          <t>178018</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>537942</t>
+          <t>315895</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44630; 73943</t>
+          <t>45208; 74742</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>63209; 98135</t>
+          <t>64328; 100599</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78788; 116984</t>
+          <t>80625; 115618</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>161269; 666980</t>
+          <t>117517; 160348</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>106273; 143700</t>
+          <t>106853; 145506</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>101736; 142381</t>
+          <t>103396; 146065</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>104953; 143881</t>
+          <t>103762; 144244</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>143019; 190360</t>
+          <t>158326; 194780</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>161073; 209366</t>
+          <t>158951; 205991</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177510; 231270</t>
+          <t>175042; 229281</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>195113; 249619</t>
+          <t>194195; 249244</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>336447; 969010</t>
+          <t>288191; 346568</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175705</t>
+          <t>182551</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>204687</t>
+          <t>228888</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>380392</t>
+          <t>411439</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>94054; 129287</t>
+          <t>93356; 127697</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>84193; 121900</t>
+          <t>86313; 121331</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94956; 135609</t>
+          <t>95201; 135688</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156905; 198650</t>
+          <t>160494; 203757</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>116772; 156454</t>
+          <t>117098; 154978</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>174676; 219183</t>
+          <t>174107; 218602</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>159371; 203524</t>
+          <t>158616; 204187</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>189213; 222124</t>
+          <t>210176; 248791</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>222334; 275859</t>
+          <t>222282; 272683</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>268887; 327409</t>
+          <t>268817; 328915</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>263454; 326154</t>
+          <t>263330; 325338</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>354418; 409147</t>
+          <t>384408; 441449</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>116237</t>
+          <t>126131</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>192278</t>
+          <t>209365</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>308515</t>
+          <t>335495</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>96832; 129558</t>
+          <t>96383; 128471</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>114379; 152066</t>
+          <t>116271; 152432</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>95484; 129110</t>
+          <t>94630; 129739</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>103274; 130869</t>
+          <t>111072; 140903</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>193346; 227553</t>
+          <t>191666; 225514</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>198992; 235276</t>
+          <t>198376; 235011</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>177117; 216758</t>
+          <t>176071; 217758</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>77926; 296148</t>
+          <t>194666; 222752</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>297966; 348874</t>
+          <t>296883; 344916</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>322666; 375313</t>
+          <t>322491; 377130</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>282797; 337427</t>
+          <t>285005; 337940</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>165739; 398959</t>
+          <t>314341; 357208</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>160759</t>
+          <t>175920</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>328160</t>
+          <t>356648</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>488919</t>
+          <t>532568</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>126934; 153984</t>
+          <t>126361; 152708</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>158402; 188788</t>
+          <t>159020; 190636</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>143159; 170712</t>
+          <t>143648; 173092</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>148353; 173863</t>
+          <t>162520; 190972</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>253835; 283381</t>
+          <t>254344; 283717</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>309877; 340252</t>
+          <t>308434; 339148</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>278802; 319052</t>
+          <t>280033; 318923</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>315801; 338472</t>
+          <t>343234; 369589</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>387611; 429286</t>
+          <t>390865; 429787</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>478221; 522580</t>
+          <t>477245; 522040</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>434021; 482680</t>
+          <t>433355; 483751</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>470967; 506944</t>
+          <t>512852; 552087</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>932665</t>
+          <t>743776</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1025315</t>
+          <t>1127063</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1957981</t>
+          <t>1870839</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>474454; 560810</t>
+          <t>481030; 562924</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>569321; 661015</t>
+          <t>563457; 658834</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>525968; 616499</t>
+          <t>524766; 611561</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>726198; 1480569</t>
+          <t>697179; 789609</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>868738; 973390</t>
+          <t>869194; 978300</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>978146; 1093802</t>
+          <t>978744; 1093225</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>875309; 985535</t>
+          <t>867949; 987318</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>833870; 1116157</t>
+          <t>1081305; 1176427</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1362956; 1504916</t>
+          <t>1371871; 1505426</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1581308; 1725508</t>
+          <t>1581783; 1722356</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1422095; 1562434</t>
+          <t>1417794; 1563877</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1721211; 2611019</t>
+          <t>1801687; 1939504</t>
         </is>
       </c>
     </row>
